--- a/sequences/fastseq_conditions_15.xlsx
+++ b/sequences/fastseq_conditions_15.xlsx
@@ -544,11 +544,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_36.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -560,27 +560,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
     </row>
@@ -632,35 +632,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_35.jpg</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>3</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>7</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/ball/ball_35.jpg</t>
         </is>
       </c>
     </row>
@@ -720,27 +720,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_36.jpg</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>8</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_14.jpg</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -816,35 +816,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>7</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_05.jpg</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>8</v>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
     </row>
@@ -896,19 +896,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_36.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -920,11 +920,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -992,27 +992,27 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_35.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>3</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>7</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
     </row>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1104,11 +1104,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
     </row>
@@ -1168,11 +1168,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/ball/ball_35.jpg</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1184,19 +1184,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1248,35 +1248,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>7</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>8</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_14.jpg</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
     </row>
@@ -1344,35 +1344,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
     </row>
@@ -1424,19 +1424,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>7</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_14.jpg</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1456,45 +1456,45 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_28.jpg</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
     </row>
@@ -1528,28 +1528,28 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_05.jpg</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_16.jpg</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="M13" t="n">
         <v>5</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_35.jpg</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_03.png</t>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
     </row>
@@ -1600,19 +1600,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1624,11 +1624,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1712,19 +1712,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1784,19 +1784,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1808,11 +1808,11 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
     </row>
@@ -1872,11 +1872,11 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/ball/ball_35.jpg</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1888,53 +1888,53 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_26.jpg</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_05.jpg</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_35.jpg</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_26.jpg</t>
-        </is>
-      </c>
-      <c r="M17" t="n">
-        <v>5</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
     </row>
@@ -1952,27 +1952,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>7</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>8</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_14.jpg</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
     </row>
@@ -2048,36 +2048,36 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>3</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>7</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_05.jpg</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>8</v>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_03.png</t>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
     </row>
@@ -2128,27 +2128,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>7</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>8</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_14.jpg</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2160,11 +2160,11 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -2224,19 +2224,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2248,11 +2248,11 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
     </row>
@@ -2304,27 +2304,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>7</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_14.jpg</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>8</v>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
     </row>
@@ -2392,11 +2392,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2408,28 +2408,28 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_16.jpg</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_05.jpg</t>
-        </is>
-      </c>
-      <c r="M23" t="n">
-        <v>8</v>
-      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_03.png</t>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
     </row>
@@ -2480,27 +2480,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_36.jpg</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="I24" t="n">
         <v>8</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_14.jpg</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2512,11 +2512,11 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
     </row>
@@ -2576,19 +2576,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2600,11 +2600,11 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -2664,11 +2664,11 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2752,11 +2752,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/ball/ball_35.jpg</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2776,11 +2776,11 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2840,11 +2840,11 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2928,11 +2928,11 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2952,11 +2952,11 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3008,35 +3008,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_36.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_14.jpg</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="I30" t="n">
         <v>5</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>2</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
     </row>
@@ -3096,44 +3096,44 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_05.jpg</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_35.jpg</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_27.jpg</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="K31" t="n">
         <v>5</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_05.jpg</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_35.jpg</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_16.jpg</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>3</v>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_01.png</t>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
     </row>
@@ -3184,19 +3184,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3208,11 +3208,11 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3288,27 +3288,27 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -3368,11 +3368,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -3384,11 +3384,11 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
     </row>
@@ -3456,11 +3456,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3480,11 +3480,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
     </row>
@@ -3536,35 +3536,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>7</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_14.jpg</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="K36" t="n">
         <v>8</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_07.jpg</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_14.jpg</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>5</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
     </row>
@@ -3624,77 +3624,77 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>stimuli/hand/hand_05.jpg</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>8</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_27.jpg</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_16.jpg</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="M37" t="n">
         <v>5</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_05.jpg</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>8</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_16.jpg</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
         <is>
           <t>stimuli/hammer/hammer_27.jpg</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>7</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_35.jpg</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
     </row>
@@ -3712,27 +3712,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>7</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_14.jpg</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>8</v>
-      </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3816,19 +3816,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -3888,11 +3888,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3920,11 +3920,11 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -3984,11 +3984,11 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/ball/ball_35.jpg</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4000,19 +4000,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/ball/ball_35.jpg</t>
         </is>
       </c>
     </row>
@@ -4072,19 +4072,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_36.jpg</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="I42" t="n">
         <v>8</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_14.jpg</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>5</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -4096,11 +4096,11 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -4160,11 +4160,11 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4184,11 +4184,11 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -4240,19 +4240,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_36.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -4264,11 +4264,11 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
     </row>
@@ -4336,11 +4336,11 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
+          <t>stimuli/ball/ball_35.jpg</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -4352,53 +4352,53 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_26.jpg</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>5</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_35.jpg</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_16.jpg</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
-        <v>3</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
     </row>
@@ -4424,36 +4424,36 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_36.jpg</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>7</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="I46" t="n">
         <v>8</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_14.jpg</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>5</v>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_07.jpg</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>2</v>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_28.jpg</t>
-        </is>
-      </c>
-      <c r="M46" t="n">
-        <v>3</v>
-      </c>
       <c r="N46" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_02.png</t>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
     </row>
@@ -4512,11 +4512,11 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4536,11 +4536,11 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -4592,19 +4592,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="G48" t="n">
         <v>7</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_14.jpg</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>8</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_36.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
     </row>
@@ -4696,28 +4696,28 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_16.jpg</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
         <v>7</v>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_05.jpg</t>
-        </is>
-      </c>
-      <c r="M49" t="n">
-        <v>8</v>
-      </c>
       <c r="N49" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_05.png</t>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
     </row>
@@ -4768,11 +4768,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_36.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4784,61 +4784,61 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_14.jpg</t>
+          <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>2</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_28.jpg</t>
-        </is>
-      </c>
-      <c r="M50" t="n">
-        <v>3</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
     </row>
@@ -4856,35 +4856,35 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_35.jpg</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="I51" t="n">
         <v>2</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>3</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>7</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
     </row>
@@ -4944,35 +4944,35 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
         <v>7</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_14.jpg</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>8</v>
-      </c>
       <c r="H52" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_14.jpg</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>2</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>stimuli/bicycle/bicycle_38.jpg</t>
+          <t>stimuli/ball/ball_07.jpg</t>
         </is>
       </c>
     </row>
@@ -5032,11 +5032,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5048,61 +5048,61 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_27.jpg</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>7</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_26.jpg</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>5</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_03.png</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_01.png</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_04.png</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_00.png</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_02.png</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>stimuli/mask_images/mask_05.png</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
           <t>stimuli/hand/hand_05.jpg</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>8</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_35.jpg</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_16.jpg</t>
-        </is>
-      </c>
-      <c r="M53" t="n">
-        <v>3</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_03.png</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_01.png</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_04.png</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_00.png</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_02.png</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>stimuli/mask_images/mask_05.png</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
     </row>
@@ -5120,35 +5120,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
         <v>7</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_14.jpg</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="K54" t="n">
         <v>8</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_07.jpg</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_14.jpg</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>5</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_36.jpg</t>
+          <t>stimuli/bread/bread_28.jpg</t>
         </is>
       </c>
     </row>
@@ -5208,11 +5208,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5224,28 +5224,28 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_16.jpg</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>7</v>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_05.jpg</t>
-        </is>
-      </c>
-      <c r="M55" t="n">
-        <v>8</v>
-      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>stimuli/mask_images/mask_05.png</t>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
     </row>
@@ -5296,19 +5296,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
         <v>7</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_14.jpg</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>8</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -5320,11 +5320,11 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -5400,19 +5400,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_35.jpg</t>
+          <t>stimuli/dog/dog_26.jpg</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -5472,19 +5472,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_07.jpg</t>
+          <t>stimuli/dog/dog_14.jpg</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_14.jpg</t>
+          <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -5576,11 +5576,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -5592,11 +5592,11 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>stimuli/hand/hand_05.jpg</t>
+          <t>stimuli/hammer/hammer_27.jpg</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
     </row>
@@ -5648,35 +5648,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_28.jpg</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_36.jpg</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="G60" t="n">
         <v>7</v>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_14.jpg</t>
         </is>
       </c>
-      <c r="G60" t="n">
+      <c r="I60" t="n">
         <v>8</v>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_14.jpg</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>5</v>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_28.jpg</t>
+          <t>stimuli/bicycle/bicycle_38.jpg</t>
         </is>
       </c>
     </row>
@@ -5752,27 +5752,27 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_27.jpg</t>
+          <t>stimuli/bread/bread_16.jpg</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_16.jpg</t>
+          <t>stimuli/bicycle/bicycle_33.jpg</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_26.jpg</t>
+          <t>stimuli/hand/hand_05.jpg</t>
         </is>
       </c>
     </row>
